--- a/Codes_2025/Trial 3/Trial3_LR_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_LR_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>5.93</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53388020614059</v>
+        <v>14.14524541628988</v>
       </c>
       <c r="E2" t="n">
-        <v>11.60388020614059</v>
+        <v>8.215245416289884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>2.64</v>
       </c>
       <c r="D3" t="n">
-        <v>15.23975195045385</v>
+        <v>15.69353349666888</v>
       </c>
       <c r="E3" t="n">
-        <v>12.59975195045385</v>
+        <v>13.05353349666888</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         <v>10.68</v>
       </c>
       <c r="D4" t="n">
-        <v>9.917977006653036</v>
+        <v>10.27418827065693</v>
       </c>
       <c r="E4" t="n">
-        <v>0.762022993346962</v>
+        <v>0.4058117293430641</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>7.740000000000002</v>
       </c>
       <c r="D5" t="n">
-        <v>12.90942269103414</v>
+        <v>11.65077923893839</v>
       </c>
       <c r="E5" t="n">
-        <v>5.169422691034134</v>
+        <v>3.910779238938391</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>37.81</v>
+        <v>19.89</v>
       </c>
       <c r="D6" t="n">
-        <v>17.26674680088729</v>
+        <v>14.27478362535645</v>
       </c>
       <c r="E6" t="n">
-        <v>20.54325319911271</v>
+        <v>5.615216374643545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>6.81</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D7" t="n">
-        <v>18.62042892384936</v>
+        <v>12.02636602289723</v>
       </c>
       <c r="E7" t="n">
-        <v>11.81042892384936</v>
+        <v>3.976366022897226</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>19.89</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>18.14824428380296</v>
+        <v>13.53519666481861</v>
       </c>
       <c r="E8" t="n">
-        <v>1.741755716197037</v>
+        <v>5.545196664818611</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>8.050000000000002</v>
+        <v>28.09</v>
       </c>
       <c r="D9" t="n">
-        <v>12.38631105773945</v>
+        <v>11.02888096201464</v>
       </c>
       <c r="E9" t="n">
-        <v>4.336311057739445</v>
+        <v>17.06111903798536</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>7.989999999999999</v>
+        <v>33.88</v>
       </c>
       <c r="D10" t="n">
-        <v>15.69041040756772</v>
+        <v>9.584107035590756</v>
       </c>
       <c r="E10" t="n">
-        <v>7.700410407567717</v>
+        <v>24.29589296440925</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>28.09</v>
+        <v>5.56</v>
       </c>
       <c r="D11" t="n">
-        <v>12.37889888993993</v>
+        <v>12.57923026738456</v>
       </c>
       <c r="E11" t="n">
-        <v>15.71110111006006</v>
+        <v>7.019230267384564</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,94 +703,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>33.88</v>
+        <v>11.6</v>
       </c>
       <c r="D12" t="n">
-        <v>7.76802510751098</v>
+        <v>11.27548524220419</v>
       </c>
       <c r="E12" t="n">
-        <v>26.11197489248902</v>
+        <v>0.3245147577958125</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24.26000000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>18.66721381233542</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.592786187664583</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D14" t="n">
-        <v>15.34124618380123</v>
-      </c>
-      <c r="E14" t="n">
-        <v>9.78124618380123</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.71353927167643</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.113539271676427</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
